--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,6 +620,7 @@
       <c r="T2" t="n">
         <v>10.55</v>
       </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +707,7 @@
       <c r="T3" t="n">
         <v>14.39</v>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -787,6 +794,7 @@
       <c r="T4" t="n">
         <v>14.84</v>
       </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -873,6 +881,7 @@
       <c r="T5" t="n">
         <v>-100</v>
       </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -959,6 +968,7 @@
       <c r="T6" t="n">
         <v>16.38</v>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1045,6 +1055,7 @@
       <c r="T7" t="n">
         <v>18.27</v>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1131,6 +1142,7 @@
       <c r="T8" t="n">
         <v>16.97</v>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1140,83 +1152,169 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COPA SUDAMERICANA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Santos x Atletico MG</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Atletico MG</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>29</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>200</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>USA 1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps x LA Galaxy</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Vancouver Whitecaps</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Match Odds (Draw)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>LAY</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>6.4</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>1.36</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>18.52</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>100</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>3x0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>0.95</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>0.95</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>17.59</v>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-09.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1204,19 +1204,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S9" t="n">
